--- a/layers/bike_lanes/manual/lookup_bikelane_types.xlsx
+++ b/layers/bike_lanes/manual/lookup_bikelane_types.xlsx
@@ -1,26 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">facility_text</t>
   </si>
@@ -52,7 +44,7 @@
     <t xml:space="preserve">Protected</t>
   </si>
   <si>
-    <t xml:space="preserve">Curbside Buffered </t>
+    <t xml:space="preserve">Curbside Buffered</t>
   </si>
   <si>
     <t xml:space="preserve">Conventional Buffered</t>
@@ -107,37 +99,32 @@
   </si>
   <si>
     <t xml:space="preserve">Curbside Buffered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conventional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conventional Buffered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wide Parking Lane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unpaved</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -149,7 +136,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -157,445 +144,525 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B1048576"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.21"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+    <row r="3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+    <row r="4">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="10">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="B10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="B11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+    <row r="14">
+      <c r="A14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="15">
+      <c r="A15" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+    <row r="16">
+      <c r="A16" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+    <row r="17">
+      <c r="A17" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+    <row r="19">
+      <c r="A19" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+    <row r="21">
+      <c r="A21" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="22">
+      <c r="A22" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="B22"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="B23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+    <row r="25">
+      <c r="A25" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>